--- a/光伏配储项目/电价数据/2026/疏港站.xlsx
+++ b/光伏配储项目/电价数据/2026/疏港站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.3141600000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.26497</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.16143</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.16024</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.18598</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07331</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.07687999999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17102</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25231</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25693</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24159</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.16955</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.03213</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.17203</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.10007</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.80864</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.03044</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.0179</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7605599999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.12913</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.45329</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.45588</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.13553</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.4801</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.31764</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.22397</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.48874</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.09562999999999999</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.18726</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.65427</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.61498</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.46713</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.14985</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.19266</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.08265</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.00591</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.27509</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26211</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.63335</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.77467</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.74412</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.76683</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.7672</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.82021</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.8321499999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02822</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.80462</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.5875900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78925</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.81511</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78122</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.80116</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46293</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.7526799999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32486</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.24853</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.26482</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.10511</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.15647</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22707</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.04805</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.25907</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.26806</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.73934</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7641</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.79223</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.22502</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.25047</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.14454</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20671</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.43176</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.05385</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45828</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51228</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51285</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.50451</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5437000000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.52665</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6279199999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70592</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.42131</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50151</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50578</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.64161</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.42716</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.45286</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47064</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.47911</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42913</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.49252</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.32977</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.06623999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.78792</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.06968000000000001</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.07647</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.10694</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.02775</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19075</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12428</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.04618999999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.07701999999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66814</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50244</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.25554</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14356</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10421</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02929</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3183</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.07296</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24741</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25282</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.03642</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.06247</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19599</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25218</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.05728</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25084</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21872</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19684</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25202</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20573</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20637</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04935</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19406</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06052</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05873</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31639</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.63458</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7694299999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87038</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65776</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5736599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40536</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.45908</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.26491</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.5971599999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26705</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.18265</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18386</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26397</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26351</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32452</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.78752</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.19852</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.27684</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.05231</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.06252000000000001</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.09978000000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.008960000000000001</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.02244</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.04853</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>-0.03933</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.04878</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.20842</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.06456000000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.06112</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.03014</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.08186</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.07793000000000001</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.04914</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.02519</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.19216</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.13506</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.22978</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.05143</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.13729</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.2385</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.23939</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.04293</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.24607</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.20379</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.21739</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.03744</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.12719</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.01255</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.03008</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.18035</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>-0.03294</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.03532</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.05895</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.09886</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.19603</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.23895</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.24808</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.04076</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.25487</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.02732</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.04528</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.06627</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.06295000000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.06108</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.06244</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.05698</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.08348</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.06219</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.04956</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.09157999999999999</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.05994</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.06297999999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.06084000000000001</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.06870999999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.05556000000000001</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.04445</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.22012</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.04631</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.04013000000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.03539</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19221</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.01958</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18938</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.03879</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.04947</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.04837</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.02668</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19464</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04237</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.008279999999999999</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.02094</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.16072</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.12792</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.01292</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.24581</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.02218</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.11014</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.02831</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.10288</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.23566</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.03587</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.11226</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.03111</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.03127</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.17785</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.24504</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.20812</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.26549</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20473</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24168</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26005</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27106</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27209</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27238</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.26234</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28696</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28368</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.22884</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24592</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30526</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9926900000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.62718</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49344</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48466</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5367000000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.17032</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.15772</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.17728</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43605</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52661</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.09025</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>-0.04427</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.03972999999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.11912</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.61651</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.25472</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46823</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.10401</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.02039</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.04792</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.04999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.17786</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20478</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19677</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26909</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19863</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19594</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16097</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.19999</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19567</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20134</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.00134</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20846</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17446</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16559</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.16423</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.20198</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.23496</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.19914</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.26158</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.24129</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.23726</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.02229</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.23948</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.21962</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.22205</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.22993</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.18767</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.23278</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.21405</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.23318</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.19395</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.18661</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.04797</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.1793</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.19246</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.22451</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.24562</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.13921</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.24344</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.27396</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.22253</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27613</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.21063</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.20631</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.02058</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23919</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3183</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.00082</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28288</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27203</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.56621</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21264</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29869</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28763</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50404</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.59477</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60664</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74207</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.42448</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42816</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.00628</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.00504</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.21407</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5380199999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64379</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32246</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27418</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27966</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18035</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.007980000000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.00039</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.20881</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.04121</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.02408</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.01953</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.00543</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.0354</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.02837</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.19718</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.18972</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.1928</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.04737</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.27434</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.21874</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.23153</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.11809</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.03743</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.0359</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.03954</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.02837</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.16231</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>-0.00043</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.04443</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.04434</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.04424</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.10871</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.16891</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.10017</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.18143</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17433</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01211</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.24198</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.008460000000000001</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17455</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.00206</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17336</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16585</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16865</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17146</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.006549999999999999</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17426</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00637</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01772</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18739</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15584</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.24002</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04058</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24672</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.18864</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.08940000000000001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.25715</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.24636</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.18656</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15997</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.13132</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.00514</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.01266</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.01791</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.00856</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.02106</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.008919999999999999</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>-0.00189</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.15012</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.14568</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>-0.00153</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.15008</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.17429</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.02029</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.11383</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.15213</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22542</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.04478</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25114</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.19738</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.22621</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22253</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.08878</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.22641</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.06854</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.19764</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-0.00233</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.19802</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.20596</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.24982</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05272</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19005</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18701</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26845</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.00209</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20596</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22624</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21811</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01313</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00014</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20065</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01362</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18069</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01312</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01312</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00383</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24557</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03628</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00633</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2207</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.09128</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20018</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.20595</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.20057</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.20168</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.0008399999999999999</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.17871</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24012</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25448</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24014</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27225</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17681</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17136</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17581</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17311</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02129</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15766</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.02041</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.02278</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.02008</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20019</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20016</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8505900000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8617999999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09264</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.0007099999999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00161</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06881999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47502</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.66059</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5061600000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.43373</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74282</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.83466</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.56899</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.62378</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7127</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.71092</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.71412</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.79092</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31039</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27633</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19894</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26256</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25103</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22017</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26827</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20785</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17426</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20334</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16859</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17134</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.02184</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18949</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23837</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24706</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25671</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29428</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.15855</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44893</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7206699999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.75309</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.43933</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.50574</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6517000000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.7569199999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20291</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31872</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.5781900000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.63905</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5505599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32331</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.02224</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27215</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43323</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20021</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43546</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.54272</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.20588</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.47432</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32749</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.65654</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.18843</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27692</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.05889</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.05556000000000001</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.21345</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.00553</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.22757</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33945</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23007</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17608</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19863</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14612</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12159</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14394</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14529</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18817</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26666</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22824</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.08231000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.19851</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.21808</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.14212</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24219</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.28098</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.22874</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.17722</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.14967</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.08857</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.24014</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.05479999999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.0007700000000000001</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.00313</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.04857</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.07476000000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.05963</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.34445</v>
       </c>
     </row>
   </sheetData>
